--- a/saldo_menor/sinais_saldo_menor_2026-08-08.xlsx
+++ b/saldo_menor/sinais_saldo_menor_2026-08-08.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/saldo_menor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="11_4A05385317A86AB58C4816D04B5ED87656CDE92D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DC89261-A612-4FF8-A6FB-8563CA8B25F4}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="11_4A05385317A86AB58C4816D04B5ED87656CDE92D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08CAE380-C327-4EB9-99BD-646B4D0F391D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="71">
   <si>
     <t>Data</t>
   </si>
@@ -71,9 +71,6 @@
   </si>
   <si>
     <t>🟢 Betmines: X2 &amp; UNDER 2.5 (Placar: 0x0 ou 1x1 | Confiança 67.6%)</t>
-  </si>
-  <si>
-    <t>APROVADO_SALDO_MENOR</t>
   </si>
   <si>
     <t>05:00</t>
@@ -243,7 +240,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -299,7 +296,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -315,6 +312,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -689,22 +690,22 @@
         <v>46242</v>
       </c>
       <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
         <v>18</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>20</v>
       </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H3">
         <v>2.5</v>
@@ -716,7 +717,7 @@
         <v>1.91</v>
       </c>
       <c r="K3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -730,22 +731,22 @@
         <v>46242</v>
       </c>
       <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
       <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
         <v>23</v>
       </c>
-      <c r="E4" t="s">
-        <v>24</v>
-      </c>
       <c r="F4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" t="s">
         <v>23</v>
-      </c>
-      <c r="G4" t="s">
-        <v>24</v>
       </c>
       <c r="H4">
         <v>1.85</v>
@@ -757,7 +758,7 @@
         <v>1.79</v>
       </c>
       <c r="K4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -771,22 +772,22 @@
         <v>46242</v>
       </c>
       <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
         <v>18</v>
       </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
       <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
         <v>26</v>
       </c>
-      <c r="E5" t="s">
-        <v>27</v>
-      </c>
       <c r="F5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
         <v>26</v>
-      </c>
-      <c r="G5" t="s">
-        <v>27</v>
       </c>
       <c r="H5">
         <v>2.37</v>
@@ -798,7 +799,7 @@
         <v>1.79</v>
       </c>
       <c r="K5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L5">
         <v>1</v>
@@ -812,22 +813,22 @@
         <v>46242</v>
       </c>
       <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
         <v>29</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>30</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>31</v>
       </c>
-      <c r="E6" t="s">
-        <v>32</v>
-      </c>
       <c r="F6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H6">
         <v>2.35</v>
@@ -839,7 +840,7 @@
         <v>1.39</v>
       </c>
       <c r="K6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -853,22 +854,22 @@
         <v>46242</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
       </c>
       <c r="D7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" t="s">
         <v>35</v>
       </c>
-      <c r="E7" t="s">
-        <v>36</v>
-      </c>
       <c r="F7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" t="s">
         <v>35</v>
-      </c>
-      <c r="G7" t="s">
-        <v>36</v>
       </c>
       <c r="H7">
         <v>1.96</v>
@@ -880,7 +881,7 @@
         <v>1.61</v>
       </c>
       <c r="K7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L7">
         <v>1</v>
@@ -894,22 +895,22 @@
         <v>46242</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
       </c>
       <c r="D8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" t="s">
         <v>38</v>
       </c>
-      <c r="E8" t="s">
-        <v>39</v>
-      </c>
       <c r="F8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" t="s">
         <v>38</v>
-      </c>
-      <c r="G8" t="s">
-        <v>39</v>
       </c>
       <c r="H8">
         <v>2.4</v>
@@ -921,7 +922,7 @@
         <v>1.65</v>
       </c>
       <c r="K8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L8">
         <v>1</v>
@@ -935,22 +936,22 @@
         <v>46242</v>
       </c>
       <c r="B9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" t="s">
         <v>41</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>42</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>43</v>
       </c>
-      <c r="E9" t="s">
-        <v>44</v>
-      </c>
       <c r="F9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" t="s">
         <v>43</v>
-      </c>
-      <c r="G9" t="s">
-        <v>44</v>
       </c>
       <c r="H9">
         <v>2.2000000000000002</v>
@@ -962,7 +963,7 @@
         <v>1.25</v>
       </c>
       <c r="K9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L9">
         <v>1</v>
@@ -976,22 +977,22 @@
         <v>46242</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>
       </c>
       <c r="D10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" t="s">
         <v>46</v>
       </c>
-      <c r="E10" t="s">
-        <v>47</v>
-      </c>
       <c r="F10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H10">
         <v>2.4</v>
@@ -1003,7 +1004,7 @@
         <v>1.65</v>
       </c>
       <c r="K10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L10">
         <v>1</v>
@@ -1017,22 +1018,22 @@
         <v>46242</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
       </c>
       <c r="D11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" t="s">
         <v>49</v>
       </c>
-      <c r="E11" t="s">
-        <v>50</v>
-      </c>
       <c r="F11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" t="s">
         <v>49</v>
-      </c>
-      <c r="G11" t="s">
-        <v>50</v>
       </c>
       <c r="H11">
         <v>2.35</v>
@@ -1044,7 +1045,7 @@
         <v>1.47</v>
       </c>
       <c r="K11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L11">
         <v>1</v>
@@ -1058,22 +1059,22 @@
         <v>46242</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
       </c>
       <c r="D12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" t="s">
         <v>52</v>
       </c>
-      <c r="E12" t="s">
-        <v>53</v>
-      </c>
       <c r="F12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H12">
         <v>2.4</v>
@@ -1085,7 +1086,7 @@
         <v>1.7</v>
       </c>
       <c r="K12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L12">
         <v>1</v>
@@ -1099,22 +1100,22 @@
         <v>46242</v>
       </c>
       <c r="B13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" t="s">
         <v>54</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>55</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>56</v>
       </c>
-      <c r="E13" t="s">
-        <v>57</v>
-      </c>
       <c r="F13" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" t="s">
         <v>56</v>
-      </c>
-      <c r="G13" t="s">
-        <v>57</v>
       </c>
       <c r="H13">
         <v>2.15</v>
@@ -1126,7 +1127,7 @@
         <v>1.96</v>
       </c>
       <c r="K13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L13">
         <v>1</v>
@@ -1140,22 +1141,22 @@
         <v>46242</v>
       </c>
       <c r="B14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" t="s">
         <v>59</v>
       </c>
-      <c r="C14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>60</v>
       </c>
-      <c r="E14" t="s">
-        <v>61</v>
-      </c>
       <c r="F14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H14">
         <v>2.5499999999999998</v>
@@ -1167,7 +1168,7 @@
         <v>1.35</v>
       </c>
       <c r="K14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L14">
         <v>1</v>
@@ -1181,22 +1182,22 @@
         <v>46242</v>
       </c>
       <c r="B15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" t="s">
         <v>63</v>
       </c>
-      <c r="C15" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>64</v>
       </c>
-      <c r="E15" t="s">
-        <v>65</v>
-      </c>
       <c r="F15" t="s">
+        <v>63</v>
+      </c>
+      <c r="G15" t="s">
         <v>64</v>
-      </c>
-      <c r="G15" t="s">
-        <v>65</v>
       </c>
       <c r="H15">
         <v>2.4</v>
@@ -1208,9 +1209,12 @@
         <v>1.47</v>
       </c>
       <c r="K15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
         <v>1</v>
       </c>
     </row>
@@ -1219,22 +1223,22 @@
         <v>46242</v>
       </c>
       <c r="B16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" t="s">
         <v>67</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>68</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>69</v>
       </c>
-      <c r="E16" t="s">
-        <v>70</v>
-      </c>
       <c r="F16" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" t="s">
         <v>69</v>
-      </c>
-      <c r="G16" t="s">
-        <v>70</v>
       </c>
       <c r="H16">
         <v>2.25</v>
@@ -1246,10 +1250,13 @@
         <v>1.79</v>
       </c>
       <c r="K16" t="s">
-        <v>71</v>
-      </c>
-      <c r="L16" t="s">
-        <v>17</v>
+        <v>70</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
